--- a/artfynd/S 2840-2025 artfynd.xlsx
+++ b/artfynd/S 2840-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ56"/>
+  <dimension ref="A1:AZ71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3379,10 +3379,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>112177922</v>
+        <v>137457173</v>
       </c>
       <c r="B26" t="n">
-        <v>89138</v>
+        <v>93485</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3390,38 +3390,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4404</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sotvaxskivling</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hygrophorus camarophyllus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Dumée &amp; al.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Skrivarhällsmyran, Skrivarhällsmyran, Dlr</t>
+          <t>Stora Skånan S, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>542789</v>
+        <v>542913</v>
       </c>
       <c r="R26" t="n">
-        <v>6680740</v>
+        <v>6680653</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3445,12 +3444,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2023-09-18</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2023-09-18</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3461,31 +3460,36 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>barrnaturskog</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Veronica Jägbrant</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Åke Persson, Stig-Åke Svenson, Sture Lindstrand</t>
+          <t>Veronica Jägbrant</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112177922</t>
+          <t>https://artportalen.se/Sighting/137457173</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120477934</v>
+        <v>137457174</v>
       </c>
       <c r="B27" t="n">
-        <v>91930</v>
+        <v>93485</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3493,43 +3497,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5442</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Skrivarhällsmyran, Skrivarhällsmyran, Dlr</t>
+          <t>Stora Skånan S, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>542876</v>
+        <v>542893</v>
       </c>
       <c r="R27" t="n">
-        <v>6680554</v>
+        <v>6680591</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3556,22 +3551,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>14:36</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>14:36</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3582,31 +3567,36 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>barrnaturskog</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Veronica Jägbrant</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Veronica Jägbrant</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120477934</t>
+          <t>https://artportalen.se/Sighting/137457174</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120477983</v>
+        <v>137457177</v>
       </c>
       <c r="B28" t="n">
-        <v>91930</v>
+        <v>93485</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3614,45 +3604,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5442</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Skrivarhällsmyran, Skrivarhällsmyran, Dlr</t>
+          <t>Stora Skånan S, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>542905</v>
+        <v>542859</v>
       </c>
       <c r="R28" t="n">
-        <v>6680571</v>
+        <v>6680591</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3679,22 +3658,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>14:41</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>14:41</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3703,34 +3672,38 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>barrnaturskog</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Veronica Jägbrant</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Veronica Jägbrant</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120477983</t>
+          <t>https://artportalen.se/Sighting/137457177</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>112175318</v>
+        <v>137457181</v>
       </c>
       <c r="B29" t="n">
-        <v>93235</v>
+        <v>93485</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3738,38 +3711,40 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Skrivarhällsmyran, Skrivarhällsmyran, Dlr</t>
+          <t>Stora Skånan S, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>542788</v>
+        <v>542889</v>
       </c>
       <c r="R29" t="n">
-        <v>6680758</v>
+        <v>6680766</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3793,12 +3768,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2023-09-18</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2023-09-18</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3807,33 +3782,39 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>barrnaturskog</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Veronica Jägbrant</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Åke Persson, Stig-Åke Svenson, Sture Lindstrand</t>
+          <t>Veronica Jägbrant</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112175318</t>
+          <t>https://artportalen.se/Sighting/137457181</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120474097</v>
+        <v>137457184</v>
       </c>
       <c r="B30" t="n">
-        <v>93235</v>
+        <v>93485</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3841,43 +3822,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Skrivarhällsmyran, Skrivarhällsmyran, Dlr</t>
+          <t>Stora Skånan S, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>542727</v>
+        <v>542732</v>
       </c>
       <c r="R30" t="n">
-        <v>6680741</v>
+        <v>6680742</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3904,22 +3876,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>12:26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>12:26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3930,31 +3892,36 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>barrnaturskog</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Veronica Jägbrant</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Veronica Jägbrant</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120474097</t>
+          <t>https://artportalen.se/Sighting/137457184</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120476979</v>
+        <v>137457185</v>
       </c>
       <c r="B31" t="n">
-        <v>93235</v>
+        <v>93485</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3962,34 +3929,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Skrivarhällsmyran, Skrivarhällsmyran, Dlr</t>
+          <t>Stora Skånan S, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>542905</v>
+        <v>542737</v>
       </c>
       <c r="R31" t="n">
-        <v>6680663</v>
+        <v>6680785</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4016,22 +3983,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>14:08</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>14:08</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4042,31 +3999,36 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>barrnaturskog</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Veronica Jägbrant</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Veronica Jägbrant</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120476979</t>
+          <t>https://artportalen.se/Sighting/137457185</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120478117</v>
+        <v>112177922</v>
       </c>
       <c r="B32" t="n">
-        <v>93235</v>
+        <v>89138</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4074,37 +4036,38 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5966</v>
+        <v>4404</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Sotvaxskivling</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hygrophorus camarophyllus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Alb. &amp; Schwein.) Dumée &amp; al.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Skrivarhällsmyran, Skrivarhällsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>542920</v>
+        <v>542789</v>
       </c>
       <c r="R32" t="n">
-        <v>6680610</v>
+        <v>6680740</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4128,22 +4091,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>14:56</t>
+          <t>2023-09-18</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>14:56</t>
+          <t>2023-09-18</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4158,27 +4111,27 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Patric Engfeldt, Åke Persson, Stig-Åke Svenson, Sture Lindstrand</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120478117</t>
+          <t>https://artportalen.se/Sighting/112177922</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120478175</v>
+        <v>120477934</v>
       </c>
       <c r="B33" t="n">
-        <v>93235</v>
+        <v>91930</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4186,41 +4139,43 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5966</v>
+        <v>5442</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Skrivarhällsmyran, Skrivarhällsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>542902</v>
+        <v>542876</v>
       </c>
       <c r="R33" t="n">
-        <v>6680638</v>
+        <v>6680554</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4252,7 +4207,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4262,7 +4217,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4271,7 +4226,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4289,55 +4243,65 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120478175</t>
+          <t>https://artportalen.se/Sighting/120477934</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>112178474</v>
+        <v>120477983</v>
       </c>
       <c r="B34" t="n">
-        <v>92567</v>
+        <v>91930</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6031</v>
+        <v>5442</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Skrivarhällsmyran, Skrivarhällsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>542893</v>
+        <v>542905</v>
       </c>
       <c r="R34" t="n">
-        <v>6680772</v>
+        <v>6680571</v>
       </c>
       <c r="S34" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4361,12 +4325,22 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2023-09-18</t>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2023-09-18</t>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4375,75 +4349,72 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Åke Persson, Stig-Åke Svenson, Sture Lindstrand</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112178474</t>
+          <t>https://artportalen.se/Sighting/120477983</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130318115</v>
+        <v>137457176</v>
       </c>
       <c r="B35" t="n">
-        <v>57806</v>
+        <v>92206</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100020</v>
+        <v>5442</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Berguv</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Bubo bubo</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Skrivarhällarna / Skånan, Dlr</t>
+          <t>Stora Skånan S, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>542813</v>
+        <v>542891</v>
       </c>
       <c r="R35" t="n">
-        <v>6680882</v>
+        <v>6680559</v>
       </c>
       <c r="S35" t="n">
-        <v>75</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4467,12 +4438,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4483,74 +4454,80 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>gammal tall</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Göran Rönning</t>
+          <t>Veronica Jägbrant</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Göran Rönning</t>
+          <t>Veronica Jägbrant</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130318115</t>
+          <t>https://artportalen.se/Sighting/137457176</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120473811</v>
+        <v>112175318</v>
       </c>
       <c r="B36" t="n">
-        <v>57950</v>
+        <v>93235</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="K36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Skrivarhällsmyran, Skrivarhällsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>542777</v>
+        <v>542788</v>
       </c>
       <c r="R36" t="n">
-        <v>6680833</v>
+        <v>6680758</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4574,22 +4551,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>12:15</t>
+          <t>2023-09-18</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>12:15</t>
+          <t>2023-09-18</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4604,55 +4571,59 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Patric Engfeldt, Åke Persson, Stig-Åke Svenson, Sture Lindstrand</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120473811</t>
+          <t>https://artportalen.se/Sighting/112175318</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120476478</v>
+        <v>120474097</v>
       </c>
       <c r="B37" t="n">
-        <v>57950</v>
+        <v>93235</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4661,10 +4632,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>542734</v>
+        <v>542727</v>
       </c>
       <c r="R37" t="n">
-        <v>6680708</v>
+        <v>6680741</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4696,7 +4667,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4706,7 +4677,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4732,56 +4703,51 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120476478</t>
+          <t>https://artportalen.se/Sighting/120474097</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120476553</v>
+        <v>120476979</v>
       </c>
       <c r="B38" t="n">
-        <v>57950</v>
+        <v>93235</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Skrivarhällsmyran, Skrivarhällsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>542745</v>
+        <v>542905</v>
       </c>
       <c r="R38" t="n">
-        <v>6680632</v>
+        <v>6680663</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4813,7 +4779,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4823,7 +4789,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4849,56 +4815,51 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120476553</t>
+          <t>https://artportalen.se/Sighting/120476979</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120476987</v>
+        <v>120478117</v>
       </c>
       <c r="B39" t="n">
-        <v>57950</v>
+        <v>93235</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Skrivarhällsmyran, Skrivarhällsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>542905</v>
+        <v>542920</v>
       </c>
       <c r="R39" t="n">
-        <v>6680663</v>
+        <v>6680610</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4930,7 +4891,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4940,7 +4901,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4966,16 +4927,16 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120476987</t>
+          <t>https://artportalen.se/Sighting/120478117</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120473757</v>
+        <v>120478175</v>
       </c>
       <c r="B40" t="n">
-        <v>57953</v>
+        <v>93235</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4983,39 +4944,41 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>5966</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Skrivarhällsmyran, Skrivarhällsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>542816</v>
+        <v>542902</v>
       </c>
       <c r="R40" t="n">
-        <v>6680877</v>
+        <v>6680638</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5047,7 +5010,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5057,7 +5020,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5066,6 +5029,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5083,16 +5047,16 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120473757</t>
+          <t>https://artportalen.se/Sighting/120478175</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>117375977</v>
+        <v>112178474</v>
       </c>
       <c r="B41" t="n">
-        <v>57754</v>
+        <v>92567</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5100,49 +5064,38 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>102118</v>
+        <v>6031</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Nattskärra</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Caprimulgus europaeus</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Skrivarhällsmyran V, Dlr</t>
+          <t>Skrivarhällsmyran, Skrivarhällsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>542860</v>
+        <v>542893</v>
       </c>
       <c r="R41" t="n">
-        <v>6680660</v>
+        <v>6680772</v>
       </c>
       <c r="S41" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5166,17 +5119,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2023-09-18</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Observatör Kjell Bergkvist Falun.</t>
+          <t>2023-09-18</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5191,27 +5139,27 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Via Lars-Erik Nilsson</t>
+          <t>Patric Engfeldt, Åke Persson, Stig-Åke Svenson, Sture Lindstrand</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117375977</t>
+          <t>https://artportalen.se/Sighting/112178474</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>112178014</v>
+        <v>137457186</v>
       </c>
       <c r="B42" t="n">
-        <v>58114</v>
+        <v>78938</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5219,38 +5167,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>103021</v>
+        <v>6437</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Skrivarhällsmyran, Skrivarhällsmyran, Dlr</t>
+          <t>Stora Skånan S, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>542883</v>
+        <v>542736</v>
       </c>
       <c r="R42" t="n">
-        <v>6680792</v>
+        <v>6680791</v>
       </c>
       <c r="S42" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5274,12 +5221,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2023-09-18</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2023-09-18</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5290,70 +5237,79 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>silverstubbe</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Veronica Jägbrant</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Åke Persson, Stig-Åke Svenson, Sture Lindstrand</t>
+          <t>Veronica Jägbrant</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112178014</t>
+          <t>https://artportalen.se/Sighting/137457186</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>112175707</v>
+        <v>137457175</v>
       </c>
       <c r="B43" t="n">
-        <v>8455</v>
+        <v>80154</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Skrivarhällsmyran, Skrivarhällsmyran, Dlr</t>
+          <t>Stora Skånan S, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>542751</v>
+        <v>542889</v>
       </c>
       <c r="R43" t="n">
-        <v>6680690</v>
+        <v>6680586</v>
       </c>
       <c r="S43" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5377,12 +5333,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2023-09-18</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2023-09-18</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5393,70 +5349,83 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>låg silverstubbe</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Veronica Jägbrant</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Åke Persson, Stig-Åke Svenson, Sture Lindstrand</t>
+          <t>Veronica Jägbrant</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112175707</t>
+          <t>https://artportalen.se/Sighting/137457175</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>112175782</v>
+        <v>130318115</v>
       </c>
       <c r="B44" t="n">
-        <v>8455</v>
+        <v>57806</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>106545</v>
+        <v>100020</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Berguv</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Bubo bubo</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Skrivarhällsmyran, Skrivarhällsmyran, Dlr</t>
+          <t>Skrivarhällarna / Skånan, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>542713</v>
+        <v>542813</v>
       </c>
       <c r="R44" t="n">
-        <v>6680670</v>
+        <v>6680882</v>
       </c>
       <c r="S44" t="n">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5480,12 +5449,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2023-09-18</t>
+          <t>2025-12-27</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2023-09-18</t>
+          <t>2025-12-27</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5500,27 +5469,27 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Göran Rönning</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Åke Persson, Stig-Åke Svenson, Sture Lindstrand</t>
+          <t>Göran Rönning</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112175782</t>
+          <t>https://artportalen.se/Sighting/130318115</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120473881</v>
+        <v>120473811</v>
       </c>
       <c r="B45" t="n">
-        <v>8455</v>
+        <v>57950</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5528,27 +5497,27 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5628,16 +5597,16 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120473881</t>
+          <t>https://artportalen.se/Sighting/120473811</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120474198</v>
+        <v>120476478</v>
       </c>
       <c r="B46" t="n">
-        <v>8455</v>
+        <v>57950</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5645,27 +5614,27 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5674,13 +5643,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>542732</v>
+        <v>542734</v>
       </c>
       <c r="R46" t="n">
-        <v>6680746</v>
+        <v>6680708</v>
       </c>
       <c r="S46" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5709,7 +5678,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5719,7 +5688,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5745,16 +5714,16 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120474198</t>
+          <t>https://artportalen.se/Sighting/120476478</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120476280</v>
+        <v>120476553</v>
       </c>
       <c r="B47" t="n">
-        <v>8455</v>
+        <v>57950</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5762,27 +5731,27 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5791,10 +5760,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>542734</v>
+        <v>542745</v>
       </c>
       <c r="R47" t="n">
-        <v>6680708</v>
+        <v>6680632</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5826,7 +5795,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5836,7 +5805,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5862,16 +5831,16 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120476280</t>
+          <t>https://artportalen.se/Sighting/120476553</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120476523</v>
+        <v>120476987</v>
       </c>
       <c r="B48" t="n">
-        <v>8455</v>
+        <v>57950</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5879,27 +5848,27 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -5908,10 +5877,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>542745</v>
+        <v>542905</v>
       </c>
       <c r="R48" t="n">
-        <v>6680632</v>
+        <v>6680663</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5943,7 +5912,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5953,7 +5922,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5979,44 +5948,44 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120476523</t>
+          <t>https://artportalen.se/Sighting/120476987</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120476625</v>
+        <v>120473757</v>
       </c>
       <c r="B49" t="n">
-        <v>8455</v>
+        <v>57953</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -6025,10 +5994,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>542764</v>
+        <v>542816</v>
       </c>
       <c r="R49" t="n">
-        <v>6680666</v>
+        <v>6680877</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6060,7 +6029,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6070,7 +6039,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6096,16 +6065,16 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120476625</t>
+          <t>https://artportalen.se/Sighting/120473757</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120476885</v>
+        <v>137457180</v>
       </c>
       <c r="B50" t="n">
-        <v>8455</v>
+        <v>57221</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6113,39 +6082,42 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Skrivarhällsmyran, Skrivarhällsmyran, Dlr</t>
+          <t>Stora Skånan S, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>542900</v>
+        <v>542879</v>
       </c>
       <c r="R50" t="n">
-        <v>6680741</v>
+        <v>6680707</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6172,22 +6144,17 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>14:01</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>14:01</t>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>tjädertupp stöttes</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6198,31 +6165,36 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>barrnaturskog</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Veronica Jägbrant</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Veronica Jägbrant</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120476885</t>
+          <t>https://artportalen.se/Sighting/137457180</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120477285</v>
+        <v>137457187</v>
       </c>
       <c r="B51" t="n">
-        <v>8455</v>
+        <v>57221</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6230,39 +6202,35 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Skrivarhällsmyran, Skrivarhällsmyran, Dlr</t>
+          <t>Stora Skånan S, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>542892</v>
+        <v>542774</v>
       </c>
       <c r="R51" t="n">
-        <v>6680638</v>
+        <v>6680853</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6289,22 +6257,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>14:11</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>14:11</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6315,31 +6273,41 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>spillning på häll, trolig spelplats</t>
+        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Veronica Jägbrant</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Veronica Jägbrant</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120477285</t>
+          <t>https://artportalen.se/Sighting/137457187</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120477602</v>
+        <v>117375977</v>
       </c>
       <c r="B52" t="n">
-        <v>8455</v>
+        <v>57754</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6347,42 +6315,49 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>106545</v>
+        <v>102118</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Nattskärra</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Caprimulgus europaeus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Skrivarhällsmyran, Skrivarhällsmyran, Dlr</t>
+          <t>Skrivarhällsmyran V, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>542883</v>
+        <v>542860</v>
       </c>
       <c r="R52" t="n">
-        <v>6680608</v>
+        <v>6680660</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6406,22 +6381,17 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>14:20</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>14:20</t>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Observatör Kjell Bergkvist Falun.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6436,70 +6406,66 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Via Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120477602</t>
+          <t>https://artportalen.se/Sighting/117375977</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120478090</v>
+        <v>112178014</v>
       </c>
       <c r="B53" t="n">
-        <v>8455</v>
+        <v>58114</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="K53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Skrivarhällsmyran, Skrivarhällsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>542920</v>
+        <v>542883</v>
       </c>
       <c r="R53" t="n">
-        <v>6680596</v>
+        <v>6680792</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6523,22 +6489,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>14:53</t>
+          <t>2023-09-18</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>14:53</t>
+          <t>2023-09-18</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6553,24 +6509,24 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Patric Engfeldt, Åke Persson, Stig-Åke Svenson, Sture Lindstrand</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120478090</t>
+          <t>https://artportalen.se/Sighting/112178014</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120478134</v>
+        <v>112175707</v>
       </c>
       <c r="B54" t="n">
         <v>8455</v>
@@ -6599,24 +6555,20 @@
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="K54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Skrivarhällsmyran, Skrivarhällsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>542911</v>
+        <v>542751</v>
       </c>
       <c r="R54" t="n">
-        <v>6680628</v>
+        <v>6680690</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6640,22 +6592,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>14:56</t>
+          <t>2023-09-18</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>14:56</t>
+          <t>2023-09-18</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6670,27 +6612,27 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Patric Engfeldt, Åke Persson, Stig-Åke Svenson, Sture Lindstrand</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120478134</t>
+          <t>https://artportalen.se/Sighting/112175707</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120473817</v>
+        <v>112175782</v>
       </c>
       <c r="B55" t="n">
-        <v>58085</v>
+        <v>8455</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6698,37 +6640,38 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>205976</v>
+        <v>106545</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Skrivarhällsmyran, Skrivarhällsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>542777</v>
+        <v>542713</v>
       </c>
       <c r="R55" t="n">
-        <v>6680833</v>
+        <v>6680670</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6752,22 +6695,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>12:15</t>
+          <t>2023-09-18</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>12:15</t>
+          <t>2023-09-18</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6782,62 +6715,67 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Patric Engfeldt, Åke Persson, Stig-Åke Svenson, Sture Lindstrand</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120473817</t>
+          <t>https://artportalen.se/Sighting/112175782</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120478154</v>
+        <v>120473881</v>
       </c>
       <c r="B56" t="n">
-        <v>91402</v>
+        <v>8455</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>256703</v>
+        <v>106545</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Skrivarhällsmyran, Skrivarhällsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>542902</v>
+        <v>542777</v>
       </c>
       <c r="R56" t="n">
-        <v>6680638</v>
+        <v>6680833</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6869,7 +6807,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6879,7 +6817,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6904,6 +6842,1729 @@
       </c>
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120473881</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>120474198</v>
+      </c>
+      <c r="B57" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Skrivarhällsmyran, Skrivarhällsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>542732</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6680746</v>
+      </c>
+      <c r="S57" t="n">
+        <v>1</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120474198</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>120476280</v>
+      </c>
+      <c r="B58" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Skrivarhällsmyran, Skrivarhällsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>542734</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6680708</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120476280</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>120476523</v>
+      </c>
+      <c r="B59" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Skrivarhällsmyran, Skrivarhällsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>542745</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6680632</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120476523</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>120476625</v>
+      </c>
+      <c r="B60" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Skrivarhällsmyran, Skrivarhällsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>542764</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6680666</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120476625</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>120476885</v>
+      </c>
+      <c r="B61" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Skrivarhällsmyran, Skrivarhällsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>542900</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6680741</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120476885</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>120477285</v>
+      </c>
+      <c r="B62" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Skrivarhällsmyran, Skrivarhällsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>542892</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6680638</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120477285</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>120477602</v>
+      </c>
+      <c r="B63" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Skrivarhällsmyran, Skrivarhällsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>542883</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6680608</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120477602</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>120478090</v>
+      </c>
+      <c r="B64" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Skrivarhällsmyran, Skrivarhällsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>542920</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6680596</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120478090</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>120478134</v>
+      </c>
+      <c r="B65" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Skrivarhällsmyran, Skrivarhällsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>542911</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6680628</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120478134</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>137457178</v>
+      </c>
+      <c r="B66" t="n">
+        <v>8470</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Stora Skånan S, Dlr</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>542851</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6680616</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI66" t="inlineStr">
+        <is>
+          <t>barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>tallåga</t>
+        </is>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Veronica Jägbrant</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Veronica Jägbrant</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137457178</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>137457182</v>
+      </c>
+      <c r="B67" t="n">
+        <v>8470</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Stora Skånan S, Dlr</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>542757</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6680679</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI67" t="inlineStr">
+        <is>
+          <t>barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AO67" t="inlineStr">
+        <is>
+          <t>tallåga</t>
+        </is>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Veronica Jägbrant</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Veronica Jägbrant</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137457182</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>137457183</v>
+      </c>
+      <c r="B68" t="n">
+        <v>8470</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Stora Skånan S, Dlr</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>542699</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6680668</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI68" t="inlineStr">
+        <is>
+          <t>barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>torrtall</t>
+        </is>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Veronica Jägbrant</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Veronica Jägbrant</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137457183</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>120473817</v>
+      </c>
+      <c r="B69" t="n">
+        <v>58085</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>205976</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Gråkråka</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Corvus corone cornix</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Skrivarhällsmyran, Skrivarhällsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>542777</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6680833</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120473817</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>137457179</v>
+      </c>
+      <c r="B70" t="n">
+        <v>99351</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Stora Skånan S, Dlr</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>542868</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6680658</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI70" t="inlineStr">
+        <is>
+          <t>barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Veronica Jägbrant</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Veronica Jägbrant</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137457179</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>120478154</v>
+      </c>
+      <c r="B71" t="n">
+        <v>91402</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>256703</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Tallfingersvamp</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Ramaria eosanguinea</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Skrivarhällsmyran, Skrivarhällsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>542902</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6680638</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/120478154</t>
         </is>
@@ -6966,6 +8627,21 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 2840-2025 artfynd.xlsx
+++ b/artfynd/S 2840-2025 artfynd.xlsx
@@ -3382,7 +3382,7 @@
         <v>137457173</v>
       </c>
       <c r="B26" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3489,7 +3489,7 @@
         <v>137457174</v>
       </c>
       <c r="B27" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3596,7 +3596,7 @@
         <v>137457177</v>
       </c>
       <c r="B28" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         <v>137457181</v>
       </c>
       <c r="B29" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3814,7 +3814,7 @@
         <v>137457184</v>
       </c>
       <c r="B30" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3921,7 +3921,7 @@
         <v>137457185</v>
       </c>
       <c r="B31" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4376,7 +4376,7 @@
         <v>137457176</v>
       </c>
       <c r="B35" t="n">
-        <v>92206</v>
+        <v>92210</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5159,7 +5159,7 @@
         <v>137457186</v>
       </c>
       <c r="B42" t="n">
-        <v>78938</v>
+        <v>78942</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5271,7 +5271,7 @@
         <v>137457175</v>
       </c>
       <c r="B43" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6074,7 +6074,7 @@
         <v>137457180</v>
       </c>
       <c r="B50" t="n">
-        <v>57221</v>
+        <v>57224</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6194,7 +6194,7 @@
         <v>137457187</v>
       </c>
       <c r="B51" t="n">
-        <v>57221</v>
+        <v>57224</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -8356,7 +8356,7 @@
         <v>137457179</v>
       </c>
       <c r="B70" t="n">
-        <v>99351</v>
+        <v>99355</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
